--- a/artfynd/A 22174-2022 artfynd.xlsx
+++ b/artfynd/A 22174-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22174-2022 artfynd.xlsx
+++ b/artfynd/A 22174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118903227</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100017</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Giljemyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>389331</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6683098</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22174-2022 artfynd.xlsx
+++ b/artfynd/A 22174-2022 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>118903227</v>
       </c>
       <c r="B3" t="n">
-        <v>100017</v>
+        <v>100024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 22174-2022 artfynd.xlsx
+++ b/artfynd/A 22174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84915510</v>
+        <v>95562116</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vitsand distrikt, Torsby kommun, Svealand, Värmlands län, Vrm</t>
+          <t>Torsby, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389292.8903272201</v>
+        <v>389313</v>
       </c>
       <c r="R2" t="n">
-        <v>6682990.394888968</v>
+        <v>6683012</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-04-28</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-04-28</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118903227</v>
+        <v>119441436</v>
       </c>
       <c r="B3" t="n">
-        <v>100029</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,31 +805,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -838,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389331</v>
+        <v>389306</v>
       </c>
       <c r="R3" t="n">
-        <v>6683098</v>
+        <v>6682967</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,12 +873,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,6 +902,338 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>71111824</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Traktorväg3 Giljemyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>389298</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6682955</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-05-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-05-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Minst 200 plantor i ca 7 olika bestånd längs en sträcka på ca 50m. Traktorväg, östsluttning</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>84915510</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vitsand distrikt, Torsby kommun, Svealand, Värmlands län, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>389293</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6682990</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-04-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-04-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118903227</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Giljemyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>389331</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6683098</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22174-2022 artfynd.xlsx
+++ b/artfynd/A 22174-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95562116</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119441436</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71111824</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84915510</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,8 +1259,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118903227</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>